--- a/food_beverage_order_forms/020_deli_order_form_for_in_store_pickup--food_beverage_order_forms.xlsx
+++ b/food_beverage_order_forms/020_deli_order_form_for_in_store_pickup--food_beverage_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'turkey-sandwich',_'label':_'turkey_sandwich',_'required':_true}</t>
+          <t>turkey_sandwich</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'turkey-sandwich', 'label': 'Turkey Sandwich', 'required': True}</t>
+          <t>Turkey Sandwich</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'ham-sandwich',_'label':_'ham_sandwich',_'required':_false}</t>
+          <t>ham_sandwich</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'ham-sandwich', 'label': 'Ham Sandwich', 'required': False}</t>
+          <t>Ham Sandwich</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'chicken-sandwich',_'label':_'chicken_sandwich',_'required':_false}</t>
+          <t>chicken_sandwich</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'chicken-sandwich', 'label': 'Chicken Sandwich', 'required': False}</t>
+          <t>Chicken Sandwich</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'garden-salad',_'label':_'garden_salad',_'required':_true}</t>
+          <t>garden_salad</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'garden-salad', 'label': 'Garden Salad', 'required': True}</t>
+          <t>Garden Salad</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'caesar-salad',_'label':_'caesar_salad',_'required':_false}</t>
+          <t>caesar_salad</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'caesar-salad', 'label': 'Caesar Salad', 'required': False}</t>
+          <t>Caesar Salad</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'water',_'label':_'water',_'required':_false}</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'water', 'label': 'Water', 'required': False}</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'soda',_'label':_'soda',_'required':_false}</t>
+          <t>soda</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'soda', 'label': 'Soda', 'required': False}</t>
+          <t>Soda</t>
         </is>
       </c>
     </row>
